--- a/backend/petty_cash_template.xlsx
+++ b/backend/petty_cash_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://10xds-my.sharepoint.com/personal/anitta_shaji_10xds_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{E9F255BB-8456-4E14-ACB2-4ADA8AEA7E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C827571-488E-4142-955B-AC210605593C}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{E9F255BB-8456-4E14-ACB2-4ADA8AEA7E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5623186C-ECD2-41DE-9B23-1CB249143524}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="950">
   <si>
     <t>Exponential Digital Solutions Pvt. Ltd. Petty Cash Log</t>
   </si>
@@ -3280,7 +3280,10 @@
     <t>PC/21-22/1063</t>
   </si>
   <si>
-    <t>Closing balance on 31/Dec/2025</t>
+    <t>Deposit Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expense Category </t>
   </si>
 </sst>
 </file>
@@ -3497,7 +3500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3641,6 +3644,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3660,7 +3666,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="118">
+  <dxfs count="122">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3779,7 +3785,64 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3825,49 +3888,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3883,107 +3903,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="m/d/yyyy;@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4381,6 +4301,168 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="m/d/yyyy;@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6141,25 +6223,29 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A5:H141" totalsRowCount="1" headerRowDxfId="117" dataDxfId="116" totalsRowDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A5:H141" totalsRowCount="1" headerRowDxfId="121" dataDxfId="120" totalsRowDxfId="119">
   <autoFilter ref="A5:H140" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" totalsRowLabel="Total" dataDxfId="114" totalsRowDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Receipt No." totalsRowFunction="count" dataDxfId="112" totalsRowDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="110" totalsRowDxfId="109"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="108" totalsRowDxfId="107"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="106" totalsRowDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Charged To" dataDxfId="104" totalsRowDxfId="103"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Received By" dataDxfId="102" totalsRowDxfId="101"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Approved By" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" totalsRowLabel="Total" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Receipt No." totalsRowFunction="count" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Charged To" dataDxfId="108" totalsRowDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Received By" dataDxfId="106" totalsRowDxfId="105"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Approved By" dataDxfId="104" totalsRowDxfId="103"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A48384EA-A6F4-46DE-B0AF-4F1F3CD4DCEA}" name="Table13" displayName="Table13" ref="A5:H168" totalsRowCount="1" headerRowDxfId="98" dataDxfId="97" totalsRowDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A48384EA-A6F4-46DE-B0AF-4F1F3CD4DCEA}" name="Table13" displayName="Table13" ref="A5:H168" totalsRowCount="1" headerRowDxfId="102" dataDxfId="101" totalsRowDxfId="100">
   <autoFilter ref="A5:H167" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}">
     <filterColumn colId="6">
       <filters>
@@ -6170,83 +6256,85 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BE616882-8319-43FB-A865-22B9D3114EC1}" name="Date" totalsRowLabel="Total" dataDxfId="95" totalsRowDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{FAFC5CA0-00FC-4277-80FD-BBE8AD4846C3}" name="Receipt No." totalsRowFunction="count" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{CAB0941A-A1D1-4440-AE74-B73F1AD95925}" name="Description" dataDxfId="91" totalsRowDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{2EB20159-6E50-4C9B-A02D-8C07F68F7BD1}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{B35A686D-9438-449F-8F59-4EF996EF483A}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{412314C3-B0A6-4C50-A0E8-0FB4B4069CD5}" name="Charged To" dataDxfId="85" totalsRowDxfId="84"/>
-    <tableColumn id="7" xr3:uid="{0297D3EB-858F-4C06-AEF7-8687C624F841}" name="Received By" dataDxfId="83" totalsRowDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{260E5C16-D7ED-4A7F-A3B3-3D4785162D21}" name="Approved By" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{BE616882-8319-43FB-A865-22B9D3114EC1}" name="Date" totalsRowLabel="Total" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{FAFC5CA0-00FC-4277-80FD-BBE8AD4846C3}" name="Receipt No." totalsRowFunction="count" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="3" xr3:uid="{CAB0941A-A1D1-4440-AE74-B73F1AD95925}" name="Description" dataDxfId="95" totalsRowDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{2EB20159-6E50-4C9B-A02D-8C07F68F7BD1}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{B35A686D-9438-449F-8F59-4EF996EF483A}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{412314C3-B0A6-4C50-A0E8-0FB4B4069CD5}" name="Charged To" dataDxfId="89" totalsRowDxfId="88"/>
+    <tableColumn id="7" xr3:uid="{0297D3EB-858F-4C06-AEF7-8687C624F841}" name="Received By" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{260E5C16-D7ED-4A7F-A3B3-3D4785162D21}" name="Approved By" dataDxfId="85" totalsRowDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1318C996-0030-45AD-B17A-D423A09F4E0E}" name="Table136" displayName="Table136" ref="A5:H170" totalsRowCount="1" headerRowDxfId="79" dataDxfId="78" totalsRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1318C996-0030-45AD-B17A-D423A09F4E0E}" name="Table136" displayName="Table136" ref="A5:H170" totalsRowCount="1" headerRowDxfId="83" dataDxfId="82" totalsRowDxfId="81">
   <autoFilter ref="A5:H169" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{07E26EDE-0C79-4FEA-A7FE-EE1F6522C13C}" name="Date" totalsRowLabel="Total" dataDxfId="76" totalsRowDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{82B8C9D0-A416-427B-AAD3-EE1535A0919B}" name="Receipt No." totalsRowFunction="count" dataDxfId="74" totalsRowDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{4AFCA37E-3940-4FD3-9AF6-CF23397FB874}" name="Description" dataDxfId="72" totalsRowDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{1A7445C8-AA02-463A-A4C7-D3EC87584C04}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="70" totalsRowDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{7E977498-20FD-4704-BCD8-7974489EEC01}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="68" totalsRowDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{4740B721-D105-4BF0-BF55-467C9945A656}" name="Charged To" dataDxfId="66" totalsRowDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{2163A1E3-6BD4-4079-855C-66E7460DDEBA}" name="Received By" dataDxfId="64" totalsRowDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{6FA90D63-2FFF-48DD-9BC3-04E523B2D160}" name="Approved By" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{07E26EDE-0C79-4FEA-A7FE-EE1F6522C13C}" name="Date" totalsRowLabel="Total" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{82B8C9D0-A416-427B-AAD3-EE1535A0919B}" name="Receipt No." totalsRowFunction="count" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{4AFCA37E-3940-4FD3-9AF6-CF23397FB874}" name="Description" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{1A7445C8-AA02-463A-A4C7-D3EC87584C04}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{7E977498-20FD-4704-BCD8-7974489EEC01}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{4740B721-D105-4BF0-BF55-467C9945A656}" name="Charged To" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{2163A1E3-6BD4-4079-855C-66E7460DDEBA}" name="Received By" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{6FA90D63-2FFF-48DD-9BC3-04E523B2D160}" name="Approved By" dataDxfId="66" totalsRowDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CAD441DF-444D-44A0-9DAB-C584DBC62033}" name="Table1367" displayName="Table1367" ref="A5:H170" totalsRowCount="1" headerRowDxfId="60" dataDxfId="59" totalsRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CAD441DF-444D-44A0-9DAB-C584DBC62033}" name="Table1367" displayName="Table1367" ref="A5:H170" totalsRowCount="1" headerRowDxfId="64" dataDxfId="63" totalsRowDxfId="62">
   <autoFilter ref="A5:H169" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{43C49A73-C368-4D37-8749-401AD97C18A8}" name="Date" totalsRowLabel="Total" dataDxfId="57" totalsRowDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{74F53108-BAB2-4BB4-A910-CF11BE398844}" name="Receipt No." totalsRowFunction="count" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{94C08663-1A5D-4B84-9D11-6230E28A76D1}" name="Description" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{180E1224-7E8B-497F-AB7B-6C3DCE9A4A68}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A822CD7D-E124-4041-BE43-F839A84799A2}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{F54C2A50-C3C8-4702-8ADE-51768DE24331}" name="Charged To" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{67CE6F09-9A61-4D58-B055-D506392A24D7}" name="Received By" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{CB1C6611-2767-4041-BD4D-10085A1DA2B5}" name="Approved By" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{43C49A73-C368-4D37-8749-401AD97C18A8}" name="Date" totalsRowLabel="Total" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{74F53108-BAB2-4BB4-A910-CF11BE398844}" name="Receipt No." totalsRowFunction="count" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{94C08663-1A5D-4B84-9D11-6230E28A76D1}" name="Description" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{180E1224-7E8B-497F-AB7B-6C3DCE9A4A68}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{A822CD7D-E124-4041-BE43-F839A84799A2}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{F54C2A50-C3C8-4702-8ADE-51768DE24331}" name="Charged To" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{67CE6F09-9A61-4D58-B055-D506392A24D7}" name="Received By" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{CB1C6611-2767-4041-BD4D-10085A1DA2B5}" name="Approved By" dataDxfId="47" totalsRowDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7C08B608-8730-4616-B716-DDA0344BFA5B}" name="Table136789" displayName="Table136789" ref="A4:G125" totalsRowCount="1" headerRowDxfId="41" dataDxfId="40" totalsRowDxfId="39">
-  <autoFilter ref="A4:G124" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D4F3FF98-CD38-4747-9716-14329CE3E2AE}" name="Date" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{023D7934-9890-48F8-BE95-A48F2B153BFF}" name="Description" dataDxfId="18" totalsRowDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{ED653C3A-688F-40EB-898C-BE1955F9808D}" name="Deposit" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{4D7ADC8A-35DD-4ECF-9876-953F9DCB80F4}" name="Expense" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{BEE8318F-FCE5-4F94-B86E-1A615340480B}" name="Received By" dataDxfId="15" totalsRowDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2B120B31-9CE6-4F99-A238-DD45F5ABC674}" name="Balance" dataDxfId="14" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{681ABC89-4E1F-4FE0-8FF2-0EA689654658}" name="Remarks" dataDxfId="13" totalsRowDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7C08B608-8730-4616-B716-DDA0344BFA5B}" name="Table136789" displayName="Table136789" ref="A4:I123" totalsRowCount="1" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
+  <autoFilter ref="A4:I122" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{D4F3FF98-CD38-4747-9716-14329CE3E2AE}" name="Date" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{023D7934-9890-48F8-BE95-A48F2B153BFF}" name="Description" dataDxfId="41" totalsRowDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{7F9A275B-03F6-4FE0-85CA-237A15AC79AC}" name="Deposit Category" dataDxfId="9" totalsRowDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{30F05E95-F39A-4AA0-911F-AD1087F42B6B}" name="Expense Category " dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{ED653C3A-688F-40EB-898C-BE1955F9808D}" name="Deposit" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{4D7ADC8A-35DD-4ECF-9876-953F9DCB80F4}" name="Expense" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{BEE8318F-FCE5-4F94-B86E-1A615340480B}" name="Received By" dataDxfId="38" totalsRowDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{2B120B31-9CE6-4F99-A238-DD45F5ABC674}" name="Balance" dataDxfId="37" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{681ABC89-4E1F-4FE0-8FF2-0EA689654658}" name="Remarks" dataDxfId="36" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}" name="Table13678" displayName="Table13678" ref="A5:H79" totalsRowCount="1" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}" name="Table13678" displayName="Table13678" ref="A5:H79" totalsRowCount="1" headerRowDxfId="35" dataDxfId="34" totalsRowDxfId="33">
   <autoFilter ref="A5:H78" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6C471D2E-0B5A-452A-B6ED-CCD94DB24388}" name="Date" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{4044760D-E2C5-4CAD-A33A-FC9400511D3C}" name="Receipt No." totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{1A1D7094-7B4D-4A3D-8148-0ACF486BEB31}" name="Description" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{C845876E-4635-4298-8CAF-73166E87541B}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{712923C5-C482-4365-B700-EE42B97EF07F}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{D499CAC0-1638-4F65-88E2-EB74E9A0DAA9}" name="Charged To" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="1" xr3:uid="{6C471D2E-0B5A-452A-B6ED-CCD94DB24388}" name="Date" totalsRowLabel="Total" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{4044760D-E2C5-4CAD-A33A-FC9400511D3C}" name="Receipt No." totalsRowFunction="count" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{1A1D7094-7B4D-4A3D-8148-0ACF486BEB31}" name="Description" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C845876E-4635-4298-8CAF-73166E87541B}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{712923C5-C482-4365-B700-EE42B97EF07F}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{D499CAC0-1638-4F65-88E2-EB74E9A0DAA9}" name="Charged To" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="21">
       <totalsRowFormula>Table13678[[#Totals],[Amount Deposited]]-Table13678[[#Totals],[Amount Withdrawn]]</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9F872129-06CC-49AD-8CC9-B8FEE66F2CE1}" name="Received By" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{7554030C-2390-4C39-BF54-EA0ADBB62B25}" name="Approved By" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{9F872129-06CC-49AD-8CC9-B8FEE66F2CE1}" name="Received By" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{7554030C-2390-4C39-BF54-EA0ADBB62B25}" name="Approved By" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6557,15 +6645,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
@@ -6589,12 +6677,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
+      <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A6:A140),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A6:A140),"dd/mm/yyyy")</f>
         <v>For 01/04/2017 through 31/03/2018</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
@@ -6602,8 +6690,8 @@
         <f>D141-E141</f>
         <v>-3456.5800000000017</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
@@ -9887,7 +9975,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="12" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9929,15 +10017,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
         <v>292</v>
       </c>
@@ -9961,12 +10049,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
+      <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A6:A167),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A6:A167),"dd/mm/yyyy")</f>
         <v>For 01/04/2018 through 31/03/2019</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
@@ -9974,8 +10062,8 @@
         <f>D168-E168</f>
         <v>-5647</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
@@ -13797,7 +13885,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="11" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13839,15 +13927,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
         <v>596</v>
       </c>
@@ -13871,12 +13959,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
+      <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A6:A169),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A6:A169),"dd/mm/yyyy")</f>
         <v>For 01/04/2019 through 15/03/2020</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
@@ -13884,8 +13972,8 @@
         <f>D170-E170</f>
         <v>955</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
@@ -17168,7 +17256,7 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="10" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17210,15 +17298,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
         <v>826</v>
       </c>
@@ -17242,12 +17330,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
+      <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A6:A169),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A6:A169),"dd/mm/yyyy")</f>
         <v>For 01/04/2020 through 27/02/2021</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
@@ -17255,8 +17343,8 @@
         <f>D170-E170</f>
         <v>665</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
@@ -19012,7 +19100,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="9" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19034,22 +19122,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB94694-26A4-46DA-B959-9CB5E252B5FB}">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.1796875" style="5" customWidth="1"/>
-    <col min="3" max="5" width="16.7265625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="16.7265625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.1796875" style="5"/>
-    <col min="11" max="11" width="11.26953125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="9.1796875" style="5"/>
+    <col min="3" max="3" width="20.1796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.90625" style="5" customWidth="1"/>
+    <col min="5" max="7" width="16.7265625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="16.7265625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.1796875" style="5"/>
+    <col min="13" max="13" width="11.26953125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>837</v>
       </c>
@@ -19057,1307 +19147,1547 @@
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
       <c r="E1" s="45"/>
-      <c r="F1" s="41">
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="41">
         <v>2026</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
       <c r="E2" s="43"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
-        <f>"For "&amp;TEXT(MIN(A5:A124),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A5:A124),"dd/mm/yyyy")</f>
+    <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="str">
+        <f>"For "&amp;TEXT(MIN(A5:A122),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A5:A122),"dd/mm/yyyy")</f>
         <v>For 00/01/1900 through 00/01/1900</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="35">
-        <f>C125-D125</f>
+      <c r="F3" s="35">
+        <f>E123-F123</f>
         <v>0</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="35"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>949</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>838</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="F4" s="16" t="s">
         <v>839</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="G4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="H4" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="I4" s="48" t="s">
         <v>840</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
       <c r="B5" s="19"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="6" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="19"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="23" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="23"/>
-    </row>
-    <row r="8" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="19"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="23"/>
-    </row>
-    <row r="9" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="19"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="47"/>
-    </row>
-    <row r="10" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="47"/>
+    </row>
+    <row r="10" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="19"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="47"/>
-    </row>
-    <row r="11" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="19"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="47"/>
-    </row>
-    <row r="12" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="19"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="47"/>
-    </row>
-    <row r="13" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="47"/>
+    </row>
+    <row r="13" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="19"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="47"/>
-    </row>
-    <row r="14" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="47"/>
+    </row>
+    <row r="14" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="19"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="47"/>
-    </row>
-    <row r="15" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="47"/>
+    </row>
+    <row r="15" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="19"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="47"/>
-    </row>
-    <row r="16" spans="1:8" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="47"/>
+    </row>
+    <row r="16" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="19"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="47"/>
-    </row>
-    <row r="17" spans="1:7" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="47"/>
+    </row>
+    <row r="17" spans="1:9" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="19"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="47"/>
-    </row>
-    <row r="18" spans="1:7" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="47"/>
+    </row>
+    <row r="18" spans="1:9" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="19"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="47"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="47"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="19"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="47"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="47"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="19"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="47"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="47"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="19"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="47"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="47"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="19"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="47"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="47"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="19"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="47"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="47"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="19"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="47"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="47"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="19"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="47"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="47"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="19"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="47"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="47"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="19"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="47"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="47"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="19"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="47"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="47"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="19"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="47"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="47"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="19"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="47"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="47"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="19"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="47"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="47"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="19"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="47"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="47"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="19"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="47"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="47"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="19"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="47"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="47"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="19"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="19"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="19"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="19"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="19"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="19"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="19"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="19"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="19"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="19"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="19"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="19"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="19"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="19"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="19"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="19"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="19"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="19"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="19"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="19"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="19"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="19"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="19"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="19"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="19"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="47"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="19"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="19"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="40"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="1"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="19"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="47"/>
-      <c r="H63" s="1"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="47"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="19"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="40"/>
-      <c r="G64" s="47"/>
-      <c r="H64" s="1"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="19"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="47"/>
-      <c r="H65" s="1"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="19"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="40"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="19"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="1"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="47"/>
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="19"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="40"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="19"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="1"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="19"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="19"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="19"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="47"/>
-      <c r="H72" s="1"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="19"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="47"/>
-      <c r="H73" s="1"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="19"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="19"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="1"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="19"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="1"/>
-    </row>
-    <row r="77" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="47"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17"/>
       <c r="B77" s="19"/>
-      <c r="C77" s="36"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="47"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="47"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17"/>
       <c r="B78" s="19"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="47"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17"/>
       <c r="B79" s="19"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="47"/>
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17"/>
       <c r="B80" s="19"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="47"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17"/>
       <c r="B81" s="19"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="36"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="19"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="47"/>
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17"/>
       <c r="B82" s="19"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="36"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17"/>
       <c r="B83" s="19"/>
-      <c r="C83" s="36"/>
-      <c r="D83" s="36"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="1"/>
-    </row>
-    <row r="84" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="36"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="47"/>
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17"/>
       <c r="B84" s="19"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C84" s="19"/>
+      <c r="D84" s="19"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="47"/>
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17"/>
       <c r="B85" s="19"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="1"/>
-    </row>
-    <row r="86" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="47"/>
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17"/>
       <c r="B86" s="19"/>
-      <c r="C86" s="36"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="47"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17"/>
       <c r="B87" s="19"/>
-      <c r="C87" s="36"/>
-      <c r="D87" s="36"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="1"/>
-    </row>
-    <row r="88" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="19"/>
+      <c r="D87" s="19"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="47"/>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17"/>
       <c r="B88" s="19"/>
-      <c r="C88" s="36"/>
-      <c r="D88" s="36"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="1"/>
-    </row>
-    <row r="89" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="19"/>
+      <c r="D88" s="19"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="47"/>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17"/>
       <c r="B89" s="19"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="40"/>
-      <c r="G89" s="47"/>
-      <c r="H89" s="1"/>
-    </row>
-    <row r="90" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="40"/>
+      <c r="I89" s="47"/>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17"/>
       <c r="B90" s="19"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="36"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="47"/>
-      <c r="H90" s="1"/>
-    </row>
-    <row r="91" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="19"/>
+      <c r="D90" s="19"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="47"/>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17"/>
       <c r="B91" s="19"/>
-      <c r="C91" s="36"/>
-      <c r="D91" s="36"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="40"/>
-      <c r="G91" s="47"/>
-      <c r="H91" s="1"/>
-    </row>
-    <row r="92" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="36"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="40"/>
+      <c r="I91" s="47"/>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17"/>
       <c r="B92" s="19"/>
-      <c r="C92" s="36"/>
-      <c r="D92" s="36"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="47"/>
-      <c r="H92" s="1"/>
-    </row>
-    <row r="93" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="19"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="36"/>
+      <c r="G92" s="19"/>
+      <c r="H92" s="40"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17"/>
       <c r="B93" s="19"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="36"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="40"/>
-      <c r="G93" s="47"/>
-      <c r="H93" s="1"/>
-    </row>
-    <row r="94" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="19"/>
+      <c r="H93" s="40"/>
+      <c r="I93" s="47"/>
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17"/>
       <c r="B94" s="19"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="36"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="40"/>
-      <c r="G94" s="47"/>
-      <c r="H94" s="1"/>
-    </row>
-    <row r="95" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C94" s="19"/>
+      <c r="D94" s="19"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="19"/>
+      <c r="H94" s="40"/>
+      <c r="I94" s="47"/>
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17"/>
       <c r="B95" s="19"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="40"/>
-      <c r="G95" s="47"/>
-      <c r="H95" s="1"/>
-    </row>
-    <row r="96" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="19"/>
+      <c r="H95" s="40"/>
+      <c r="I95" s="47"/>
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="17"/>
       <c r="B96" s="19"/>
-      <c r="C96" s="36"/>
-      <c r="D96" s="36"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="40"/>
-      <c r="G96" s="47"/>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="97" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="19"/>
+      <c r="D96" s="19"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="40"/>
+      <c r="I96" s="47"/>
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17"/>
       <c r="B97" s="19"/>
-      <c r="C97" s="36"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="40"/>
-      <c r="G97" s="47"/>
-      <c r="H97" s="1"/>
-    </row>
-    <row r="98" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="36"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="40"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17"/>
       <c r="B98" s="19"/>
-      <c r="C98" s="36"/>
-      <c r="D98" s="36"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="40"/>
-      <c r="G98" s="47"/>
-      <c r="H98" s="1"/>
-    </row>
-    <row r="99" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="19"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="1"/>
+    </row>
+    <row r="99" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17"/>
       <c r="B99" s="19"/>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="40"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="1"/>
-    </row>
-    <row r="100" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="40"/>
+      <c r="I99" s="47"/>
+      <c r="J99" s="1"/>
+    </row>
+    <row r="100" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17"/>
       <c r="B100" s="19"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="40"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="1"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C100" s="19"/>
+      <c r="D100" s="19"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="19"/>
+      <c r="H100" s="40"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="1"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="17"/>
       <c r="B101" s="19"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="40"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="1"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C101" s="19"/>
+      <c r="D101" s="19"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="36"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="40"/>
+      <c r="I101" s="47"/>
+      <c r="J101" s="1"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="17"/>
       <c r="B102" s="19"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="40"/>
-      <c r="G102" s="47"/>
-      <c r="H102" s="1"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C102" s="19"/>
+      <c r="D102" s="19"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="19"/>
+      <c r="H102" s="40"/>
+      <c r="I102" s="47"/>
+      <c r="J102" s="1"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="17"/>
       <c r="B103" s="19"/>
-      <c r="C103" s="36"/>
-      <c r="D103" s="36"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="40"/>
-      <c r="G103" s="47"/>
-      <c r="H103" s="1"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C103" s="19"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="19"/>
+      <c r="H103" s="40"/>
+      <c r="I103" s="47"/>
+      <c r="J103" s="1"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="17"/>
       <c r="B104" s="19"/>
-      <c r="C104" s="36"/>
-      <c r="D104" s="36"/>
-      <c r="E104" s="19"/>
-      <c r="F104" s="40"/>
-      <c r="G104" s="47"/>
-      <c r="H104" s="1"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C104" s="19"/>
+      <c r="D104" s="19"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="19"/>
+      <c r="H104" s="40"/>
+      <c r="I104" s="47"/>
+      <c r="J104" s="1"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="17"/>
       <c r="B105" s="19"/>
-      <c r="C105" s="36"/>
-      <c r="D105" s="36"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="40"/>
-      <c r="G105" s="47"/>
-      <c r="H105" s="1"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C105" s="19"/>
+      <c r="D105" s="19"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="19"/>
+      <c r="H105" s="40"/>
+      <c r="I105" s="47"/>
+      <c r="J105" s="1"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="17"/>
       <c r="B106" s="19"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="40"/>
-      <c r="G106" s="47"/>
-      <c r="H106" s="1"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C106" s="19"/>
+      <c r="D106" s="19"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+      <c r="G106" s="19"/>
+      <c r="H106" s="40"/>
+      <c r="I106" s="47"/>
+      <c r="J106" s="1"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="17"/>
       <c r="B107" s="19"/>
-      <c r="C107" s="36"/>
-      <c r="D107" s="36"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="40"/>
-      <c r="G107" s="47"/>
-      <c r="H107" s="1"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C107" s="19"/>
+      <c r="D107" s="19"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
+      <c r="G107" s="19"/>
+      <c r="H107" s="40"/>
+      <c r="I107" s="47"/>
+      <c r="J107" s="1"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="17"/>
       <c r="B108" s="19"/>
-      <c r="C108" s="36"/>
-      <c r="D108" s="36"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="40"/>
-      <c r="G108" s="47"/>
-      <c r="H108" s="1"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C108" s="19"/>
+      <c r="D108" s="19"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="40"/>
+      <c r="I108" s="47"/>
+      <c r="J108" s="1"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="17"/>
       <c r="B109" s="19"/>
-      <c r="C109" s="36"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="40"/>
-      <c r="G109" s="47"/>
-      <c r="H109" s="1"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="19"/>
+      <c r="H109" s="40"/>
+      <c r="I109" s="47"/>
+      <c r="J109" s="1"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="17"/>
       <c r="B110" s="19"/>
-      <c r="C110" s="36"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="19"/>
-      <c r="F110" s="40"/>
-      <c r="G110" s="47"/>
-      <c r="H110" s="1"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="19"/>
+      <c r="H110" s="40"/>
+      <c r="I110" s="47"/>
+      <c r="J110" s="1"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="17"/>
       <c r="B111" s="19"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="19"/>
-      <c r="F111" s="40"/>
-      <c r="G111" s="47"/>
-      <c r="H111" s="1"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+      <c r="G111" s="19"/>
+      <c r="H111" s="40"/>
+      <c r="I111" s="47"/>
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="17"/>
       <c r="B112" s="19"/>
-      <c r="C112" s="36"/>
-      <c r="D112" s="36"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="40"/>
-      <c r="G112" s="47"/>
-      <c r="H112" s="1"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C112" s="19"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="19"/>
+      <c r="H112" s="40"/>
+      <c r="I112" s="47"/>
+      <c r="J112" s="1"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="17"/>
       <c r="B113" s="19"/>
-      <c r="C113" s="36"/>
-      <c r="D113" s="36"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="40"/>
-      <c r="G113" s="47"/>
-      <c r="H113" s="1"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C113" s="19"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="19"/>
+      <c r="H113" s="40"/>
+      <c r="I113" s="47"/>
+      <c r="J113" s="1"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="17"/>
       <c r="B114" s="19"/>
-      <c r="C114" s="36"/>
-      <c r="D114" s="36"/>
-      <c r="E114" s="19"/>
-      <c r="F114" s="40"/>
-      <c r="G114" s="47"/>
-      <c r="H114" s="1"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C114" s="19"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="47"/>
+      <c r="J114" s="1"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="17"/>
       <c r="B115" s="19"/>
-      <c r="C115" s="36"/>
-      <c r="D115" s="36"/>
-      <c r="E115" s="19"/>
-      <c r="F115" s="40"/>
-      <c r="G115" s="47"/>
-      <c r="H115" s="1"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C115" s="19"/>
+      <c r="D115" s="19"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="19"/>
+      <c r="H115" s="40"/>
+      <c r="I115" s="47"/>
+      <c r="J115" s="1"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="17"/>
       <c r="B116" s="19"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="19"/>
-      <c r="F116" s="40"/>
-      <c r="G116" s="47"/>
-      <c r="H116" s="1"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C116" s="19"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="19"/>
+      <c r="H116" s="40"/>
+      <c r="I116" s="47"/>
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="17"/>
       <c r="B117" s="19"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="19"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="47"/>
-      <c r="H117" s="1"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="19"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="47"/>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="17"/>
       <c r="B118" s="19"/>
-      <c r="C118" s="36"/>
-      <c r="D118" s="36"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="40"/>
-      <c r="G118" s="47"/>
-      <c r="H118" s="1"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C118" s="19"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="40"/>
+      <c r="I118" s="47"/>
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="17"/>
       <c r="B119" s="19"/>
-      <c r="C119" s="36"/>
-      <c r="D119" s="36"/>
-      <c r="E119" s="19"/>
-      <c r="F119" s="40"/>
-      <c r="G119" s="47"/>
-      <c r="H119" s="1"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C119" s="19"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="36"/>
+      <c r="F119" s="36"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="40"/>
+      <c r="I119" s="47"/>
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="17"/>
       <c r="B120" s="19"/>
-      <c r="C120" s="36"/>
-      <c r="D120" s="36"/>
-      <c r="E120" s="19"/>
-      <c r="F120" s="40"/>
-      <c r="G120" s="47"/>
-      <c r="H120" s="1"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C120" s="19"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="36"/>
+      <c r="F120" s="36"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="40"/>
+      <c r="I120" s="47"/>
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="17"/>
       <c r="B121" s="19"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="19"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="47"/>
-      <c r="H121" s="1"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C121" s="19"/>
+      <c r="D121" s="19"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+      <c r="G121" s="19"/>
+      <c r="H121" s="40"/>
+      <c r="I121" s="47"/>
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="17"/>
       <c r="B122" s="19"/>
-      <c r="C122" s="36"/>
-      <c r="D122" s="36"/>
-      <c r="E122" s="19"/>
-      <c r="F122" s="40"/>
-      <c r="G122" s="47"/>
-      <c r="H122" s="1"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="17"/>
-      <c r="B123" s="19"/>
-      <c r="C123" s="36"/>
-      <c r="D123" s="36"/>
-      <c r="E123" s="19"/>
-      <c r="F123" s="40"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="1"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="17"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="36"/>
-      <c r="D124" s="36"/>
-      <c r="E124" s="19"/>
-      <c r="F124" s="40"/>
-      <c r="G124" s="47"/>
-      <c r="H124" s="1"/>
-    </row>
-    <row r="125" spans="1:8" ht="13" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
+      <c r="C122" s="19"/>
+      <c r="D122" s="19"/>
+      <c r="E122" s="36"/>
+      <c r="F122" s="36"/>
+      <c r="G122" s="19"/>
+      <c r="H122" s="40"/>
+      <c r="I122" s="47"/>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B125" s="3"/>
-      <c r="C125" s="37">
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="37">
         <f>SUBTOTAL(109,Table136789[Deposit])</f>
         <v>0</v>
       </c>
-      <c r="D125" s="38">
+      <c r="F123" s="38">
         <f>SUBTOTAL(109,Table136789[Expense])</f>
         <v>0</v>
       </c>
-      <c r="E125" s="38"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="46"/>
+      <c r="G123" s="38"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="46"/>
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="2"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="43"/>
+      <c r="F124" s="43"/>
+      <c r="G124" s="43"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="2"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="43"/>
+      <c r="F125" s="43"/>
+      <c r="G125" s="43"/>
       <c r="H125" s="1"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="1"/>
-      <c r="C126" s="43"/>
-      <c r="D126" s="43"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
       <c r="E126" s="43"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
+      <c r="F126" s="43"/>
+      <c r="G126" s="43"/>
       <c r="H126" s="1"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="43"/>
-      <c r="D127" s="43"/>
-      <c r="E127" s="43"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="43"/>
-      <c r="D128" s="43"/>
-      <c r="E128" s="43"/>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J128" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="D3:E3">
-    <cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F3:G3">
+    <cfRule type="cellIs" dxfId="11" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20388,15 +20718,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
         <v>841</v>
       </c>
@@ -20420,12 +20750,12 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="str">
+      <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A6:A78),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A6:A78),"dd/mm/yyyy")</f>
         <v>For 01/04/2021 through 25/03/2022</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
@@ -20433,8 +20763,8 @@
         <f>D79-E79</f>
         <v>1009</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="11"/>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
@@ -22122,7 +22452,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="7" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22150,27 +22480,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Remarks xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Paid xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">Yes</Paid>
-    <Paid_x0020_by xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Expense_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Paid_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Voucher_x0020_Ref xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Accounted xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">No</Accounted>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070022ECE254C3C4881526E01C6E38A76" ma:contentTypeVersion="27" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8f13cfbca3b99b7595aa10cd513b9af">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="1aebbf00-b20e-447e-89b2-07cb1eb45804" xmlns:ns3="c5c24acf-8734-4b59-a9c6-52f24d04b601" xmlns:ns4="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6c1da616d1348b0dfe3e056f58aa1e6" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -22496,6 +22805,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Remarks xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Paid xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">Yes</Paid>
+    <Paid_x0020_by xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Expense_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Paid_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Voucher_x0020_Ref xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Accounted xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">No</Accounted>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233E6B2D-7719-43E4-8F62-6DE1F178C0C2}">
   <ds:schemaRefs>
@@ -22505,18 +22835,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A25819BC-B8DE-4703-8E03-713856731CC1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1aebbf00-b20e-447e-89b2-07cb1eb45804"/>
-    <ds:schemaRef ds:uri="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC2D4B2A-4534-41DE-99A1-70175F0498C2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22535,4 +22853,16 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A25819BC-B8DE-4703-8E03-713856731CC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1aebbf00-b20e-447e-89b2-07cb1eb45804"/>
+    <ds:schemaRef ds:uri="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/backend/petty_cash_template.xlsx
+++ b/backend/petty_cash_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://10xds-my.sharepoint.com/personal/anitta_shaji_10xds_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{E9F255BB-8456-4E14-ACB2-4ADA8AEA7E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5623186C-ECD2-41DE-9B23-1CB249143524}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{817CF8FF-3354-4089-9C2D-E95CF51572D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AB3363F-AF08-4C39-ABF6-D78B7429BE25}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="954">
   <si>
     <t>Exponential Digital Solutions Pvt. Ltd. Petty Cash Log</t>
   </si>
@@ -2950,12 +2950,6 @@
     <t>Exponential Digital Solutions W.L.L - Petty Cash Log</t>
   </si>
   <si>
-    <t>Deposit</t>
-  </si>
-  <si>
-    <t>Expense</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -3284,6 +3278,24 @@
   </si>
   <si>
     <t xml:space="preserve">Expense Category </t>
+  </si>
+  <si>
+    <t>Original Amount-Deposite</t>
+  </si>
+  <si>
+    <t>Original Amount-Expense</t>
+  </si>
+  <si>
+    <t>Audited Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit Rate	</t>
+  </si>
+  <si>
+    <t>Final Amount</t>
+  </si>
+  <si>
+    <t>Final Rate</t>
   </si>
 </sst>
 </file>
@@ -3299,7 +3311,7 @@
     <numFmt numFmtId="169" formatCode="_ [$BHD]\ * #,##0.00_ ;_ [$BHD]\ * \-#,##0.00_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3447,6 +3459,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3500,7 +3518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3662,11 +3680,41 @@
     <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="130">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3688,6 +3736,66 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3842,7 +3950,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3903,7 +4012,229 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="m/d/yyyy;@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4301,168 +4632,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="_ [$BHD]\ * #,##0.000_ ;_ [$BHD]\ * \-#,##0.000_ ;_ [$BHD]\ * &quot;-&quot;??_ ;_ @_ "/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="m/d/yyyy;@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6223,29 +6392,25 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A5:H141" totalsRowCount="1" headerRowDxfId="121" dataDxfId="120" totalsRowDxfId="119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A5:H141" totalsRowCount="1" headerRowDxfId="129" dataDxfId="128" totalsRowDxfId="127">
   <autoFilter ref="A5:H140" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" totalsRowLabel="Total" dataDxfId="118" totalsRowDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Receipt No." totalsRowFunction="count" dataDxfId="116" totalsRowDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="114" totalsRowDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="111"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="110" totalsRowDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Charged To" dataDxfId="108" totalsRowDxfId="107"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Received By" dataDxfId="106" totalsRowDxfId="105"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Approved By" dataDxfId="104" totalsRowDxfId="103"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" totalsRowLabel="Total" dataDxfId="126" totalsRowDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Receipt No." totalsRowFunction="count" dataDxfId="124" totalsRowDxfId="123"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="122" totalsRowDxfId="121"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="120" totalsRowDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="118" totalsRowDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Charged To" dataDxfId="116" totalsRowDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Received By" dataDxfId="114" totalsRowDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Approved By" dataDxfId="112" totalsRowDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A48384EA-A6F4-46DE-B0AF-4F1F3CD4DCEA}" name="Table13" displayName="Table13" ref="A5:H168" totalsRowCount="1" headerRowDxfId="102" dataDxfId="101" totalsRowDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A48384EA-A6F4-46DE-B0AF-4F1F3CD4DCEA}" name="Table13" displayName="Table13" ref="A5:H168" totalsRowCount="1" headerRowDxfId="110" dataDxfId="109" totalsRowDxfId="108">
   <autoFilter ref="A5:H167" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}">
     <filterColumn colId="6">
       <filters>
@@ -6256,85 +6421,89 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BE616882-8319-43FB-A865-22B9D3114EC1}" name="Date" totalsRowLabel="Total" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="2" xr3:uid="{FAFC5CA0-00FC-4277-80FD-BBE8AD4846C3}" name="Receipt No." totalsRowFunction="count" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{CAB0941A-A1D1-4440-AE74-B73F1AD95925}" name="Description" dataDxfId="95" totalsRowDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{2EB20159-6E50-4C9B-A02D-8C07F68F7BD1}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{B35A686D-9438-449F-8F59-4EF996EF483A}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{412314C3-B0A6-4C50-A0E8-0FB4B4069CD5}" name="Charged To" dataDxfId="89" totalsRowDxfId="88"/>
-    <tableColumn id="7" xr3:uid="{0297D3EB-858F-4C06-AEF7-8687C624F841}" name="Received By" dataDxfId="87" totalsRowDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{260E5C16-D7ED-4A7F-A3B3-3D4785162D21}" name="Approved By" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{BE616882-8319-43FB-A865-22B9D3114EC1}" name="Date" totalsRowLabel="Total" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{FAFC5CA0-00FC-4277-80FD-BBE8AD4846C3}" name="Receipt No." totalsRowFunction="count" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{CAB0941A-A1D1-4440-AE74-B73F1AD95925}" name="Description" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="4" xr3:uid="{2EB20159-6E50-4C9B-A02D-8C07F68F7BD1}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{B35A686D-9438-449F-8F59-4EF996EF483A}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{412314C3-B0A6-4C50-A0E8-0FB4B4069CD5}" name="Charged To" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="7" xr3:uid="{0297D3EB-858F-4C06-AEF7-8687C624F841}" name="Received By" dataDxfId="95" totalsRowDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{260E5C16-D7ED-4A7F-A3B3-3D4785162D21}" name="Approved By" dataDxfId="93" totalsRowDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1318C996-0030-45AD-B17A-D423A09F4E0E}" name="Table136" displayName="Table136" ref="A5:H170" totalsRowCount="1" headerRowDxfId="83" dataDxfId="82" totalsRowDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1318C996-0030-45AD-B17A-D423A09F4E0E}" name="Table136" displayName="Table136" ref="A5:H170" totalsRowCount="1" headerRowDxfId="91" dataDxfId="90" totalsRowDxfId="89">
   <autoFilter ref="A5:H169" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{07E26EDE-0C79-4FEA-A7FE-EE1F6522C13C}" name="Date" totalsRowLabel="Total" dataDxfId="80" totalsRowDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{82B8C9D0-A416-427B-AAD3-EE1535A0919B}" name="Receipt No." totalsRowFunction="count" dataDxfId="78" totalsRowDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{4AFCA37E-3940-4FD3-9AF6-CF23397FB874}" name="Description" dataDxfId="76" totalsRowDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{1A7445C8-AA02-463A-A4C7-D3EC87584C04}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="74" totalsRowDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{7E977498-20FD-4704-BCD8-7974489EEC01}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="72" totalsRowDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{4740B721-D105-4BF0-BF55-467C9945A656}" name="Charged To" dataDxfId="70" totalsRowDxfId="69"/>
-    <tableColumn id="7" xr3:uid="{2163A1E3-6BD4-4079-855C-66E7460DDEBA}" name="Received By" dataDxfId="68" totalsRowDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{6FA90D63-2FFF-48DD-9BC3-04E523B2D160}" name="Approved By" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{07E26EDE-0C79-4FEA-A7FE-EE1F6522C13C}" name="Date" totalsRowLabel="Total" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{82B8C9D0-A416-427B-AAD3-EE1535A0919B}" name="Receipt No." totalsRowFunction="count" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{4AFCA37E-3940-4FD3-9AF6-CF23397FB874}" name="Description" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{1A7445C8-AA02-463A-A4C7-D3EC87584C04}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{7E977498-20FD-4704-BCD8-7974489EEC01}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="6" xr3:uid="{4740B721-D105-4BF0-BF55-467C9945A656}" name="Charged To" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{2163A1E3-6BD4-4079-855C-66E7460DDEBA}" name="Received By" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{6FA90D63-2FFF-48DD-9BC3-04E523B2D160}" name="Approved By" dataDxfId="74" totalsRowDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CAD441DF-444D-44A0-9DAB-C584DBC62033}" name="Table1367" displayName="Table1367" ref="A5:H170" totalsRowCount="1" headerRowDxfId="64" dataDxfId="63" totalsRowDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CAD441DF-444D-44A0-9DAB-C584DBC62033}" name="Table1367" displayName="Table1367" ref="A5:H170" totalsRowCount="1" headerRowDxfId="72" dataDxfId="71" totalsRowDxfId="70">
   <autoFilter ref="A5:H169" xr:uid="{BAA8E3C8-863B-424D-B23E-1E1562CF313C}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{43C49A73-C368-4D37-8749-401AD97C18A8}" name="Date" totalsRowLabel="Total" dataDxfId="61" totalsRowDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{74F53108-BAB2-4BB4-A910-CF11BE398844}" name="Receipt No." totalsRowFunction="count" dataDxfId="59" totalsRowDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{94C08663-1A5D-4B84-9D11-6230E28A76D1}" name="Description" dataDxfId="57" totalsRowDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{180E1224-7E8B-497F-AB7B-6C3DCE9A4A68}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{A822CD7D-E124-4041-BE43-F839A84799A2}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{F54C2A50-C3C8-4702-8ADE-51768DE24331}" name="Charged To" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{67CE6F09-9A61-4D58-B055-D506392A24D7}" name="Received By" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{CB1C6611-2767-4041-BD4D-10085A1DA2B5}" name="Approved By" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{43C49A73-C368-4D37-8749-401AD97C18A8}" name="Date" totalsRowLabel="Total" dataDxfId="69" totalsRowDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{74F53108-BAB2-4BB4-A910-CF11BE398844}" name="Receipt No." totalsRowFunction="count" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{94C08663-1A5D-4B84-9D11-6230E28A76D1}" name="Description" dataDxfId="65" totalsRowDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{180E1224-7E8B-497F-AB7B-6C3DCE9A4A68}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="63" totalsRowDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{A822CD7D-E124-4041-BE43-F839A84799A2}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{F54C2A50-C3C8-4702-8ADE-51768DE24331}" name="Charged To" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{67CE6F09-9A61-4D58-B055-D506392A24D7}" name="Received By" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{CB1C6611-2767-4041-BD4D-10085A1DA2B5}" name="Approved By" dataDxfId="55" totalsRowDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7C08B608-8730-4616-B716-DDA0344BFA5B}" name="Table136789" displayName="Table136789" ref="A4:I123" totalsRowCount="1" headerRowDxfId="45" dataDxfId="44" totalsRowDxfId="43">
-  <autoFilter ref="A4:I122" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{D4F3FF98-CD38-4747-9716-14329CE3E2AE}" name="Date" totalsRowLabel="Total" dataDxfId="42" totalsRowDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{023D7934-9890-48F8-BE95-A48F2B153BFF}" name="Description" dataDxfId="41" totalsRowDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{7F9A275B-03F6-4FE0-85CA-237A15AC79AC}" name="Deposit Category" dataDxfId="9" totalsRowDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{30F05E95-F39A-4AA0-911F-AD1087F42B6B}" name="Expense Category " dataDxfId="16" totalsRowDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{ED653C3A-688F-40EB-898C-BE1955F9808D}" name="Deposit" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{4D7ADC8A-35DD-4ECF-9876-953F9DCB80F4}" name="Expense" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{BEE8318F-FCE5-4F94-B86E-1A615340480B}" name="Received By" dataDxfId="38" totalsRowDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2B120B31-9CE6-4F99-A238-DD45F5ABC674}" name="Balance" dataDxfId="37" totalsRowDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{681ABC89-4E1F-4FE0-8FF2-0EA689654658}" name="Remarks" dataDxfId="36" totalsRowDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7C08B608-8730-4616-B716-DDA0344BFA5B}" name="Table136789" displayName="Table136789" ref="A4:M123" totalsRowCount="1" headerRowDxfId="53" dataDxfId="52" totalsRowDxfId="51">
+  <autoFilter ref="A4:M122" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{D4F3FF98-CD38-4747-9716-14329CE3E2AE}" name="Date" totalsRowLabel="Total" dataDxfId="31" totalsRowDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{023D7934-9890-48F8-BE95-A48F2B153BFF}" name="Description" dataDxfId="30" totalsRowDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{7F9A275B-03F6-4FE0-85CA-237A15AC79AC}" name="Deposit Category" dataDxfId="29" totalsRowDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{30F05E95-F39A-4AA0-911F-AD1087F42B6B}" name="Expense Category " dataDxfId="28" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{ED653C3A-688F-40EB-898C-BE1955F9808D}" name="Original Amount-Deposite" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{4D7ADC8A-35DD-4ECF-9876-953F9DCB80F4}" name="Original Amount-Expense" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{9CDF3E96-3DA8-4A2F-8C8B-CE2500CB823E}" name="Audited Amount" dataDxfId="22" totalsRowDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{38562079-FF04-4074-B3E7-605755EE7A01}" name="Audit Rate_x0009_" dataDxfId="21" totalsRowDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{7CB8C018-C3A2-44DF-B5E2-72A4CBEF5FAB}" name="Final Amount" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{6FC56BCA-726E-4B00-BD43-430FD731B5F7}" name="Final Rate" dataDxfId="14" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{BEE8318F-FCE5-4F94-B86E-1A615340480B}" name="Received By" dataDxfId="26" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{2B120B31-9CE6-4F99-A238-DD45F5ABC674}" name="Balance" dataDxfId="25" totalsRowDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{681ABC89-4E1F-4FE0-8FF2-0EA689654658}" name="Remarks" dataDxfId="24" totalsRowDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}" name="Table13678" displayName="Table13678" ref="A5:H79" totalsRowCount="1" headerRowDxfId="35" dataDxfId="34" totalsRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}" name="Table13678" displayName="Table13678" ref="A5:H79" totalsRowCount="1" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48">
   <autoFilter ref="A5:H78" xr:uid="{1284CDB2-E0A3-4052-9326-7FBF4BAEEEED}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6C471D2E-0B5A-452A-B6ED-CCD94DB24388}" name="Date" totalsRowLabel="Total" dataDxfId="32" totalsRowDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{4044760D-E2C5-4CAD-A33A-FC9400511D3C}" name="Receipt No." totalsRowFunction="count" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{1A1D7094-7B4D-4A3D-8148-0ACF486BEB31}" name="Description" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C845876E-4635-4298-8CAF-73166E87541B}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{712923C5-C482-4365-B700-EE42B97EF07F}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{D499CAC0-1638-4F65-88E2-EB74E9A0DAA9}" name="Charged To" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="1" xr3:uid="{6C471D2E-0B5A-452A-B6ED-CCD94DB24388}" name="Date" totalsRowLabel="Total" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{4044760D-E2C5-4CAD-A33A-FC9400511D3C}" name="Receipt No." totalsRowFunction="count" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{1A1D7094-7B4D-4A3D-8148-0ACF486BEB31}" name="Description" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{C845876E-4635-4298-8CAF-73166E87541B}" name="Amount Deposited" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{712923C5-C482-4365-B700-EE42B97EF07F}" name="Amount Withdrawn" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{D499CAC0-1638-4F65-88E2-EB74E9A0DAA9}" name="Charged To" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
       <totalsRowFormula>Table13678[[#Totals],[Amount Deposited]]-Table13678[[#Totals],[Amount Withdrawn]]</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9F872129-06CC-49AD-8CC9-B8FEE66F2CE1}" name="Received By" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{7554030C-2390-4C39-BF54-EA0ADBB62B25}" name="Approved By" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{9F872129-06CC-49AD-8CC9-B8FEE66F2CE1}" name="Received By" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{7554030C-2390-4C39-BF54-EA0ADBB62B25}" name="Approved By" dataDxfId="33" totalsRowDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9975,7 +10144,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="15" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13885,7 +14054,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17256,7 +17425,7 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19100,7 +19269,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="12" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19122,7 +19291,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB94694-26A4-46DA-B959-9CB5E252B5FB}">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
@@ -19139,7 +19308,7 @@
     <col min="15" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="20.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>837</v>
       </c>
@@ -19157,7 +19326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -19171,7 +19340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="str">
         <f>"For "&amp;TEXT(MIN(A5:A122),"dd/mm/yyyy")&amp;" through "&amp;TEXT(MAX(A5:A122),"dd/mm/yyyy")</f>
         <v>For 00/01/1900 through 00/01/1900</v>
@@ -19193,7 +19362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
@@ -19201,1425 +19370,1909 @@
         <v>9</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>946</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>948</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>949</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="G4" s="16" t="s">
+        <v>950</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>952</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>953</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="48" t="s">
         <v>838</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>839</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="48" t="s">
-        <v>840</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="6" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="23" t="s">
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="23"/>
-    </row>
-    <row r="8" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A9" s="17"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="47"/>
-    </row>
-    <row r="10" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="47"/>
+    </row>
+    <row r="10" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="47"/>
-    </row>
-    <row r="11" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="47"/>
+    </row>
+    <row r="11" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="47"/>
-    </row>
-    <row r="12" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="47"/>
-    </row>
-    <row r="13" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="47"/>
-    </row>
-    <row r="14" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="47"/>
-    </row>
-    <row r="15" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="16" spans="1:10" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
       <c r="E16" s="36"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="47"/>
-    </row>
-    <row r="17" spans="1:9" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="47"/>
+    </row>
+    <row r="17" spans="1:13" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="47"/>
-    </row>
-    <row r="18" spans="1:9" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="47"/>
+    </row>
+    <row r="18" spans="1:13" s="21" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="47"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="47"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="47"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="47"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="47"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="47"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="47"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="47"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="47"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="47"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="47"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="47"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="47"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="47"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="36"/>
       <c r="F25" s="36"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="47"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="47"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="47"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="47"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="36"/>
       <c r="F27" s="36"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="47"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="47"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
       <c r="E28" s="36"/>
       <c r="F28" s="36"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="47"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="47"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
       <c r="E29" s="36"/>
       <c r="F29" s="36"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="47"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="47"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="36"/>
       <c r="F30" s="36"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="47"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="47"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="36"/>
       <c r="F31" s="36"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="47"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="47"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="36"/>
       <c r="F32" s="36"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="47"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="47"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="36"/>
       <c r="F33" s="36"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="47"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="47"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="47"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="47"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
       <c r="E35" s="36"/>
       <c r="F35" s="36"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
       <c r="D36" s="19"/>
       <c r="E36" s="36"/>
       <c r="F36" s="36"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
       <c r="E37" s="36"/>
       <c r="F37" s="36"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="47"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
       <c r="D38" s="19"/>
       <c r="E38" s="36"/>
       <c r="F38" s="36"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="47"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
       <c r="E39" s="36"/>
       <c r="F39" s="36"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
       <c r="E40" s="36"/>
       <c r="F40" s="36"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="47"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
       <c r="E41" s="36"/>
       <c r="F41" s="36"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="47"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
       <c r="E42" s="36"/>
       <c r="F42" s="36"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="40"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
       <c r="E43" s="36"/>
       <c r="F43" s="36"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="47"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="36"/>
       <c r="F44" s="36"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
       <c r="E45" s="36"/>
       <c r="F45" s="36"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
       <c r="E46" s="36"/>
       <c r="F46" s="36"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="47"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
       <c r="E47" s="36"/>
       <c r="F47" s="36"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
       <c r="E48" s="36"/>
       <c r="F48" s="36"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
       <c r="E49" s="36"/>
       <c r="F49" s="36"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
       <c r="E50" s="36"/>
       <c r="F50" s="36"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
       <c r="E51" s="36"/>
       <c r="F51" s="36"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="47"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
       <c r="E52" s="36"/>
       <c r="F52" s="36"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="47"/>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="47"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
       <c r="E53" s="36"/>
       <c r="F53" s="36"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="40"/>
+      <c r="M53" s="47"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
       <c r="E54" s="36"/>
       <c r="F54" s="36"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="40"/>
+      <c r="M54" s="47"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
       <c r="E55" s="36"/>
       <c r="F55" s="36"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="47"/>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="40"/>
+      <c r="M55" s="47"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="36"/>
       <c r="F56" s="36"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="47"/>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="40"/>
+      <c r="M56" s="47"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="36"/>
       <c r="F57" s="36"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="47"/>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G57" s="36"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="36"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="40"/>
+      <c r="M57" s="47"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="36"/>
       <c r="F58" s="36"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="47"/>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="47"/>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="36"/>
       <c r="F59" s="36"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="40"/>
+      <c r="M59" s="47"/>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="36"/>
       <c r="F60" s="36"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="47"/>
-      <c r="J60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="36"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="40"/>
+      <c r="M60" s="47"/>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="47"/>
-      <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G61" s="36"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="36"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="40"/>
+      <c r="M61" s="47"/>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
       <c r="E62" s="36"/>
       <c r="F62" s="36"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="47"/>
-      <c r="J62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="36"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="40"/>
+      <c r="M62" s="47"/>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="36"/>
       <c r="F63" s="36"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="47"/>
-      <c r="J63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="36"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="40"/>
+      <c r="M63" s="47"/>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="36"/>
       <c r="F64" s="36"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="47"/>
-      <c r="J64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="36"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="40"/>
+      <c r="M64" s="47"/>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="36"/>
       <c r="F65" s="36"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="47"/>
-      <c r="J65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="47"/>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="36"/>
       <c r="F66" s="36"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="47"/>
-      <c r="J66" s="1"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G66" s="36"/>
+      <c r="H66" s="36"/>
+      <c r="I66" s="36"/>
+      <c r="J66" s="36"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="47"/>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="36"/>
       <c r="F67" s="36"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="47"/>
-      <c r="J67" s="1"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G67" s="36"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="36"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="40"/>
+      <c r="M67" s="47"/>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="36"/>
       <c r="F68" s="36"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="47"/>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="36"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="40"/>
+      <c r="M68" s="47"/>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="1"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="36"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="40"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="36"/>
       <c r="F70" s="36"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="47"/>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
+      <c r="J70" s="36"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="40"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="36"/>
       <c r="F71" s="36"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="47"/>
-      <c r="J71" s="1"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="40"/>
+      <c r="M71" s="47"/>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="47"/>
-      <c r="J72" s="1"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="40"/>
+      <c r="M72" s="47"/>
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="36"/>
       <c r="F73" s="36"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="40"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="36"/>
       <c r="F74" s="36"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="40"/>
-      <c r="I74" s="47"/>
-      <c r="J74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="40"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="36"/>
       <c r="F75" s="36"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="40"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="40"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="36"/>
       <c r="F76" s="36"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="47"/>
-      <c r="J76" s="1"/>
-    </row>
-    <row r="77" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="40"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="36"/>
       <c r="F77" s="36"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="47"/>
-      <c r="J77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="36"/>
+      <c r="K77" s="19"/>
+      <c r="L77" s="40"/>
+      <c r="M77" s="47"/>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="40"/>
-      <c r="I78" s="47"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="36"/>
+      <c r="K78" s="19"/>
+      <c r="L78" s="40"/>
+      <c r="M78" s="47"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="40"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
+      <c r="J79" s="36"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="40"/>
+      <c r="M79" s="47"/>
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="36"/>
       <c r="F80" s="36"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="47"/>
-      <c r="J80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="40"/>
+      <c r="M80" s="47"/>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="36"/>
       <c r="F81" s="36"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="47"/>
-      <c r="J81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G81" s="36"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="36"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="40"/>
+      <c r="M81" s="47"/>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="36"/>
       <c r="F82" s="36"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="47"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G82" s="36"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="36"/>
+      <c r="J82" s="36"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="40"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="36"/>
       <c r="F83" s="36"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="40"/>
-      <c r="I83" s="47"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
+      <c r="J83" s="36"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="40"/>
+      <c r="M83" s="47"/>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="17"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
       <c r="E84" s="36"/>
       <c r="F84" s="36"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36"/>
+      <c r="J84" s="36"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="40"/>
+      <c r="M84" s="47"/>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
       <c r="E85" s="36"/>
       <c r="F85" s="36"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36"/>
+      <c r="J85" s="36"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="40"/>
+      <c r="M85" s="47"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="36"/>
       <c r="F86" s="36"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="47"/>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G86" s="36"/>
+      <c r="H86" s="36"/>
+      <c r="I86" s="36"/>
+      <c r="J86" s="36"/>
+      <c r="K86" s="19"/>
+      <c r="L86" s="40"/>
+      <c r="M86" s="47"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="36"/>
       <c r="F87" s="36"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="47"/>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="40"/>
+      <c r="M87" s="47"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="36"/>
       <c r="F88" s="36"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="40"/>
-      <c r="I88" s="47"/>
-      <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36"/>
+      <c r="J88" s="36"/>
+      <c r="K88" s="19"/>
+      <c r="L88" s="40"/>
+      <c r="M88" s="47"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="40"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G89" s="36"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36"/>
+      <c r="J89" s="36"/>
+      <c r="K89" s="19"/>
+      <c r="L89" s="40"/>
+      <c r="M89" s="47"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="36"/>
       <c r="F90" s="36"/>
-      <c r="G90" s="19"/>
-      <c r="H90" s="40"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G90" s="36"/>
+      <c r="H90" s="36"/>
+      <c r="I90" s="36"/>
+      <c r="J90" s="36"/>
+      <c r="K90" s="19"/>
+      <c r="L90" s="40"/>
+      <c r="M90" s="47"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="36"/>
       <c r="F91" s="36"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="40"/>
-      <c r="I91" s="47"/>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G91" s="36"/>
+      <c r="H91" s="36"/>
+      <c r="I91" s="36"/>
+      <c r="J91" s="36"/>
+      <c r="K91" s="19"/>
+      <c r="L91" s="40"/>
+      <c r="M91" s="47"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
       <c r="E92" s="36"/>
       <c r="F92" s="36"/>
-      <c r="G92" s="19"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G92" s="36"/>
+      <c r="H92" s="36"/>
+      <c r="I92" s="36"/>
+      <c r="J92" s="36"/>
+      <c r="K92" s="19"/>
+      <c r="L92" s="40"/>
+      <c r="M92" s="47"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
       <c r="E93" s="36"/>
       <c r="F93" s="36"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="40"/>
-      <c r="I93" s="47"/>
-      <c r="J93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+      <c r="K93" s="19"/>
+      <c r="L93" s="40"/>
+      <c r="M93" s="47"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="36"/>
       <c r="F94" s="36"/>
-      <c r="G94" s="19"/>
-      <c r="H94" s="40"/>
-      <c r="I94" s="47"/>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+      <c r="K94" s="19"/>
+      <c r="L94" s="40"/>
+      <c r="M94" s="47"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
-      <c r="G95" s="19"/>
-      <c r="H95" s="40"/>
-      <c r="I95" s="47"/>
-      <c r="J95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G95" s="36"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+      <c r="K95" s="19"/>
+      <c r="L95" s="40"/>
+      <c r="M95" s="47"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="17"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
       <c r="E96" s="36"/>
       <c r="F96" s="36"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="40"/>
-      <c r="I96" s="47"/>
-      <c r="J96" s="1"/>
-    </row>
-    <row r="97" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G96" s="36"/>
+      <c r="H96" s="36"/>
+      <c r="I96" s="36"/>
+      <c r="J96" s="36"/>
+      <c r="K96" s="19"/>
+      <c r="L96" s="40"/>
+      <c r="M96" s="47"/>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
       <c r="E97" s="36"/>
       <c r="F97" s="36"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="40"/>
-      <c r="I97" s="47"/>
-      <c r="J97" s="1"/>
-    </row>
-    <row r="98" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G97" s="36"/>
+      <c r="H97" s="36"/>
+      <c r="I97" s="36"/>
+      <c r="J97" s="36"/>
+      <c r="K97" s="19"/>
+      <c r="L97" s="40"/>
+      <c r="M97" s="47"/>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="36"/>
       <c r="F98" s="36"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="40"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="1"/>
-    </row>
-    <row r="99" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G98" s="36"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="36"/>
+      <c r="K98" s="19"/>
+      <c r="L98" s="40"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="36"/>
       <c r="F99" s="36"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="40"/>
-      <c r="I99" s="47"/>
-      <c r="J99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G99" s="36"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="36"/>
+      <c r="K99" s="19"/>
+      <c r="L99" s="40"/>
+      <c r="M99" s="47"/>
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="17"/>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="36"/>
       <c r="F100" s="36"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="40"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="1"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G100" s="36"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
+      <c r="J100" s="36"/>
+      <c r="K100" s="19"/>
+      <c r="L100" s="40"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="17"/>
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="36"/>
       <c r="F101" s="36"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="40"/>
-      <c r="I101" s="47"/>
-      <c r="J101" s="1"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G101" s="36"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
+      <c r="J101" s="36"/>
+      <c r="K101" s="19"/>
+      <c r="L101" s="40"/>
+      <c r="M101" s="47"/>
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="17"/>
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="36"/>
       <c r="F102" s="36"/>
-      <c r="G102" s="19"/>
-      <c r="H102" s="40"/>
-      <c r="I102" s="47"/>
-      <c r="J102" s="1"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G102" s="36"/>
+      <c r="H102" s="36"/>
+      <c r="I102" s="36"/>
+      <c r="J102" s="36"/>
+      <c r="K102" s="19"/>
+      <c r="L102" s="40"/>
+      <c r="M102" s="47"/>
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="17"/>
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="36"/>
       <c r="F103" s="36"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="40"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="1"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G103" s="36"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="36"/>
+      <c r="J103" s="36"/>
+      <c r="K103" s="19"/>
+      <c r="L103" s="40"/>
+      <c r="M103" s="47"/>
+      <c r="N103" s="1"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="17"/>
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="36"/>
       <c r="F104" s="36"/>
-      <c r="G104" s="19"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="47"/>
-      <c r="J104" s="1"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G104" s="36"/>
+      <c r="H104" s="36"/>
+      <c r="I104" s="36"/>
+      <c r="J104" s="36"/>
+      <c r="K104" s="19"/>
+      <c r="L104" s="40"/>
+      <c r="M104" s="47"/>
+      <c r="N104" s="1"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="17"/>
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
       <c r="E105" s="36"/>
       <c r="F105" s="36"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="40"/>
-      <c r="I105" s="47"/>
-      <c r="J105" s="1"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G105" s="36"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="36"/>
+      <c r="J105" s="36"/>
+      <c r="K105" s="19"/>
+      <c r="L105" s="40"/>
+      <c r="M105" s="47"/>
+      <c r="N105" s="1"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="17"/>
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
-      <c r="G106" s="19"/>
-      <c r="H106" s="40"/>
-      <c r="I106" s="47"/>
-      <c r="J106" s="1"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G106" s="36"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="36"/>
+      <c r="J106" s="36"/>
+      <c r="K106" s="19"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="47"/>
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="17"/>
       <c r="B107" s="19"/>
       <c r="C107" s="19"/>
       <c r="D107" s="19"/>
       <c r="E107" s="36"/>
       <c r="F107" s="36"/>
-      <c r="G107" s="19"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="47"/>
-      <c r="J107" s="1"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G107" s="36"/>
+      <c r="H107" s="36"/>
+      <c r="I107" s="36"/>
+      <c r="J107" s="36"/>
+      <c r="K107" s="19"/>
+      <c r="L107" s="40"/>
+      <c r="M107" s="47"/>
+      <c r="N107" s="1"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="17"/>
       <c r="B108" s="19"/>
       <c r="C108" s="19"/>
       <c r="D108" s="19"/>
       <c r="E108" s="36"/>
       <c r="F108" s="36"/>
-      <c r="G108" s="19"/>
-      <c r="H108" s="40"/>
-      <c r="I108" s="47"/>
-      <c r="J108" s="1"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G108" s="36"/>
+      <c r="H108" s="36"/>
+      <c r="I108" s="36"/>
+      <c r="J108" s="36"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="40"/>
+      <c r="M108" s="47"/>
+      <c r="N108" s="1"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="17"/>
       <c r="B109" s="19"/>
       <c r="C109" s="19"/>
       <c r="D109" s="19"/>
       <c r="E109" s="36"/>
       <c r="F109" s="36"/>
-      <c r="G109" s="19"/>
-      <c r="H109" s="40"/>
-      <c r="I109" s="47"/>
-      <c r="J109" s="1"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G109" s="36"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36"/>
+      <c r="J109" s="36"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="40"/>
+      <c r="M109" s="47"/>
+      <c r="N109" s="1"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="17"/>
       <c r="B110" s="19"/>
       <c r="C110" s="19"/>
       <c r="D110" s="19"/>
       <c r="E110" s="36"/>
       <c r="F110" s="36"/>
-      <c r="G110" s="19"/>
-      <c r="H110" s="40"/>
-      <c r="I110" s="47"/>
-      <c r="J110" s="1"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G110" s="36"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="36"/>
+      <c r="J110" s="36"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="40"/>
+      <c r="M110" s="47"/>
+      <c r="N110" s="1"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="17"/>
       <c r="B111" s="19"/>
       <c r="C111" s="19"/>
       <c r="D111" s="19"/>
       <c r="E111" s="36"/>
       <c r="F111" s="36"/>
-      <c r="G111" s="19"/>
-      <c r="H111" s="40"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="1"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G111" s="36"/>
+      <c r="H111" s="36"/>
+      <c r="I111" s="36"/>
+      <c r="J111" s="36"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="40"/>
+      <c r="M111" s="47"/>
+      <c r="N111" s="1"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="17"/>
       <c r="B112" s="19"/>
       <c r="C112" s="19"/>
       <c r="D112" s="19"/>
       <c r="E112" s="36"/>
       <c r="F112" s="36"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="40"/>
-      <c r="I112" s="47"/>
-      <c r="J112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G112" s="36"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="36"/>
+      <c r="J112" s="36"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="40"/>
+      <c r="M112" s="47"/>
+      <c r="N112" s="1"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="17"/>
       <c r="B113" s="19"/>
       <c r="C113" s="19"/>
       <c r="D113" s="19"/>
       <c r="E113" s="36"/>
       <c r="F113" s="36"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="40"/>
-      <c r="I113" s="47"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G113" s="36"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="36"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="40"/>
+      <c r="M113" s="47"/>
+      <c r="N113" s="1"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="17"/>
       <c r="B114" s="19"/>
       <c r="C114" s="19"/>
       <c r="D114" s="19"/>
       <c r="E114" s="36"/>
       <c r="F114" s="36"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="40"/>
-      <c r="I114" s="47"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G114" s="36"/>
+      <c r="H114" s="36"/>
+      <c r="I114" s="36"/>
+      <c r="J114" s="36"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="40"/>
+      <c r="M114" s="47"/>
+      <c r="N114" s="1"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="17"/>
       <c r="B115" s="19"/>
       <c r="C115" s="19"/>
       <c r="D115" s="19"/>
       <c r="E115" s="36"/>
       <c r="F115" s="36"/>
-      <c r="G115" s="19"/>
-      <c r="H115" s="40"/>
-      <c r="I115" s="47"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G115" s="36"/>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36"/>
+      <c r="J115" s="36"/>
+      <c r="K115" s="19"/>
+      <c r="L115" s="40"/>
+      <c r="M115" s="47"/>
+      <c r="N115" s="1"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="17"/>
       <c r="B116" s="19"/>
       <c r="C116" s="19"/>
       <c r="D116" s="19"/>
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
-      <c r="G116" s="19"/>
-      <c r="H116" s="40"/>
-      <c r="I116" s="47"/>
-      <c r="J116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G116" s="36"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="36"/>
+      <c r="J116" s="36"/>
+      <c r="K116" s="19"/>
+      <c r="L116" s="40"/>
+      <c r="M116" s="47"/>
+      <c r="N116" s="1"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="17"/>
       <c r="B117" s="19"/>
       <c r="C117" s="19"/>
       <c r="D117" s="19"/>
       <c r="E117" s="36"/>
       <c r="F117" s="36"/>
-      <c r="G117" s="19"/>
-      <c r="H117" s="40"/>
-      <c r="I117" s="47"/>
-      <c r="J117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G117" s="36"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="36"/>
+      <c r="K117" s="19"/>
+      <c r="L117" s="40"/>
+      <c r="M117" s="47"/>
+      <c r="N117" s="1"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="17"/>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
       <c r="D118" s="19"/>
       <c r="E118" s="36"/>
       <c r="F118" s="36"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="47"/>
-      <c r="J118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G118" s="36"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="36"/>
+      <c r="J118" s="36"/>
+      <c r="K118" s="19"/>
+      <c r="L118" s="40"/>
+      <c r="M118" s="47"/>
+      <c r="N118" s="1"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="17"/>
       <c r="B119" s="19"/>
       <c r="C119" s="19"/>
       <c r="D119" s="19"/>
       <c r="E119" s="36"/>
       <c r="F119" s="36"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="40"/>
-      <c r="I119" s="47"/>
-      <c r="J119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G119" s="36"/>
+      <c r="H119" s="36"/>
+      <c r="I119" s="36"/>
+      <c r="J119" s="36"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="40"/>
+      <c r="M119" s="47"/>
+      <c r="N119" s="1"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="17"/>
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
       <c r="D120" s="19"/>
       <c r="E120" s="36"/>
       <c r="F120" s="36"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="40"/>
-      <c r="I120" s="47"/>
-      <c r="J120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G120" s="36"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="36"/>
+      <c r="J120" s="36"/>
+      <c r="K120" s="19"/>
+      <c r="L120" s="40"/>
+      <c r="M120" s="47"/>
+      <c r="N120" s="1"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="17"/>
       <c r="B121" s="19"/>
       <c r="C121" s="19"/>
       <c r="D121" s="19"/>
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
-      <c r="G121" s="19"/>
-      <c r="H121" s="40"/>
-      <c r="I121" s="47"/>
-      <c r="J121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G121" s="36"/>
+      <c r="H121" s="36"/>
+      <c r="I121" s="36"/>
+      <c r="J121" s="36"/>
+      <c r="K121" s="19"/>
+      <c r="L121" s="40"/>
+      <c r="M121" s="47"/>
+      <c r="N121" s="1"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="17"/>
       <c r="B122" s="19"/>
       <c r="C122" s="19"/>
       <c r="D122" s="19"/>
       <c r="E122" s="36"/>
       <c r="F122" s="36"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="40"/>
-      <c r="I122" s="47"/>
-      <c r="J122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="13" x14ac:dyDescent="0.25">
+      <c r="G122" s="36"/>
+      <c r="H122" s="36"/>
+      <c r="I122" s="36"/>
+      <c r="J122" s="36"/>
+      <c r="K122" s="19"/>
+      <c r="L122" s="40"/>
+      <c r="M122" s="47"/>
+      <c r="N122" s="1"/>
+    </row>
+    <row r="123" spans="1:14" ht="13" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>291</v>
       </c>
@@ -20627,19 +21280,23 @@
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="37">
-        <f>SUBTOTAL(109,Table136789[Deposit])</f>
+        <f>SUBTOTAL(109,Table136789[Original Amount-Deposite])</f>
         <v>0</v>
       </c>
       <c r="F123" s="38">
-        <f>SUBTOTAL(109,Table136789[Expense])</f>
+        <f>SUBTOTAL(109,Table136789[Original Amount-Expense])</f>
         <v>0</v>
       </c>
       <c r="G123" s="38"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="46"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H123" s="38"/>
+      <c r="I123" s="38"/>
+      <c r="J123" s="38"/>
+      <c r="K123" s="38"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="46"/>
+      <c r="N123" s="1"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -20651,7 +21308,7 @@
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -20663,7 +21320,7 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -20675,10 +21332,10 @@
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J128" s="1"/>
     </row>
   </sheetData>
@@ -20687,7 +21344,7 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="F3:G3">
-    <cfRule type="cellIs" dxfId="11" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20728,7 +21385,7 @@
       <c r="F1" s="52"/>
       <c r="G1" s="52"/>
       <c r="H1" s="30" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="6" t="s">
@@ -20843,7 +21500,7 @@
         <v>44294</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>295</v>
@@ -20865,10 +21522,10 @@
         <v>44296</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="20">
@@ -20876,7 +21533,7 @@
         <v>328</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>19</v>
@@ -20888,10 +21545,10 @@
         <v>44349</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="20">
@@ -20912,10 +21569,10 @@
         <v>44350</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="20">
@@ -20933,10 +21590,10 @@
         <v>44355</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="20">
@@ -20954,10 +21611,10 @@
         <v>44370</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="20">
@@ -20997,7 +21654,7 @@
         <v>44399</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>295</v>
@@ -21018,10 +21675,10 @@
         <v>44406</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="20">
@@ -21039,10 +21696,10 @@
         <v>44406</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="20">
@@ -21060,10 +21717,10 @@
         <v>44411</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="20">
@@ -21103,17 +21760,17 @@
         <v>44419</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="20">
         <v>100</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>19</v>
@@ -21124,17 +21781,17 @@
         <v>44419</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="20">
         <v>40</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="H20" s="22" t="s">
         <v>19</v>
@@ -21145,7 +21802,7 @@
         <v>44433</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>64</v>
@@ -21166,17 +21823,17 @@
         <v>44466</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D22" s="24"/>
       <c r="E22" s="20">
         <v>649</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H22" s="22" t="s">
         <v>19</v>
@@ -21187,10 +21844,10 @@
         <v>44469</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="20">
@@ -21230,17 +21887,17 @@
         <v>44473</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="20">
         <v>580</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>19</v>
@@ -21251,7 +21908,7 @@
         <v>44473</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>609</v>
@@ -21261,7 +21918,7 @@
         <v>603</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="H26" s="22" t="s">
         <v>19</v>
@@ -21272,10 +21929,10 @@
         <v>44476</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="20">
@@ -21293,7 +21950,7 @@
         <v>44476</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>295</v>
@@ -21314,10 +21971,10 @@
         <v>44476</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="20">
@@ -21357,10 +22014,10 @@
         <v>44478</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="20">
@@ -21378,10 +22035,10 @@
         <v>44487</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="20">
@@ -21399,10 +22056,10 @@
         <v>44494</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="20">
@@ -21420,10 +22077,10 @@
         <v>44494</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="20">
@@ -21441,7 +22098,7 @@
         <v>44489</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>64</v>
@@ -21462,17 +22119,17 @@
         <v>44491</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="20">
         <v>59</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>19</v>
@@ -21483,17 +22140,17 @@
         <v>44495</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="20">
         <v>500</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H37" s="22" t="s">
         <v>19</v>
@@ -21526,10 +22183,10 @@
         <v>44499</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="20">
@@ -21547,7 +22204,7 @@
         <v>44504</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>609</v>
@@ -21557,7 +22214,7 @@
         <v>594</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H40" s="22" t="s">
         <v>19</v>
@@ -21568,10 +22225,10 @@
         <v>44511</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="20">
@@ -21611,7 +22268,7 @@
         <v>44516</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>295</v>
@@ -21633,17 +22290,17 @@
         <v>44517</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="20">
         <v>366</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H44" s="22" t="s">
         <v>19</v>
@@ -21654,7 +22311,7 @@
         <v>44518</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>64</v>
@@ -21675,7 +22332,7 @@
         <v>44521</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C46" s="19" t="s">
         <v>609</v>
@@ -21685,7 +22342,7 @@
         <v>370</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H46" s="22" t="s">
         <v>19</v>
@@ -21718,10 +22375,10 @@
         <v>44531</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="20">
@@ -21739,17 +22396,17 @@
         <v>44533</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="20">
         <v>224</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H49" s="22" t="s">
         <v>19</v>
@@ -21760,7 +22417,7 @@
         <v>44533</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>295</v>
@@ -21781,17 +22438,17 @@
         <v>44534</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="20">
         <v>82</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>19</v>
@@ -21802,10 +22459,10 @@
         <v>44534</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="20">
@@ -21823,17 +22480,17 @@
         <v>44540</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="20">
         <v>59</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H53" s="22" t="s">
         <v>19</v>
@@ -21844,7 +22501,7 @@
         <v>44543</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C54" s="19" t="s">
         <v>64</v>
@@ -21866,10 +22523,10 @@
         <v>44552</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="20">
@@ -21877,7 +22534,7 @@
       </c>
       <c r="F55" s="21"/>
       <c r="G55" s="19" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H55" s="22" t="s">
         <v>19</v>
@@ -21888,7 +22545,7 @@
         <v>44552</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>609</v>
@@ -21899,7 +22556,7 @@
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="19" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H56" s="22" t="s">
         <v>19</v>
@@ -21910,10 +22567,10 @@
         <v>44552</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="20">
@@ -21921,7 +22578,7 @@
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>19</v>
@@ -21932,10 +22589,10 @@
         <v>44552</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="20">
@@ -21943,7 +22600,7 @@
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="19" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H58" s="22" t="s">
         <v>19</v>
@@ -21954,10 +22611,10 @@
         <v>44552</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="20">
@@ -21965,7 +22622,7 @@
       </c>
       <c r="F59" s="21"/>
       <c r="G59" s="19" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="H59" s="22" t="s">
         <v>19</v>
@@ -21976,10 +22633,10 @@
         <v>44560</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="20">
@@ -21987,7 +22644,7 @@
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>19</v>
@@ -21998,10 +22655,10 @@
         <v>44564</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="20">
@@ -22009,7 +22666,7 @@
       </c>
       <c r="F61" s="21"/>
       <c r="G61" s="19" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>19</v>
@@ -22020,7 +22677,7 @@
         <v>44565</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C62" s="19" t="s">
         <v>609</v>
@@ -22031,7 +22688,7 @@
       </c>
       <c r="F62" s="21"/>
       <c r="G62" s="19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H62" s="22" t="s">
         <v>19</v>
@@ -22042,10 +22699,10 @@
         <v>44566</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D63" s="24"/>
       <c r="E63" s="20">
@@ -22053,7 +22710,7 @@
       </c>
       <c r="F63" s="21"/>
       <c r="G63" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H63" s="22" t="s">
         <v>19</v>
@@ -22086,7 +22743,7 @@
         <v>44571</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>64</v>
@@ -22110,7 +22767,7 @@
         <v>44576</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>609</v>
@@ -22121,7 +22778,7 @@
       </c>
       <c r="F66" s="21"/>
       <c r="G66" s="19" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H66" s="22" t="s">
         <v>19</v>
@@ -22134,7 +22791,7 @@
         <v>44578</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C67" s="19" t="s">
         <v>295</v>
@@ -22158,7 +22815,7 @@
         <v>44581</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C68" s="19" t="s">
         <v>295</v>
@@ -22182,10 +22839,10 @@
         <v>44593</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="20">
@@ -22193,7 +22850,7 @@
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H69" s="22" t="s">
         <v>19</v>
@@ -22206,7 +22863,7 @@
         <v>44599</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C70" s="19" t="s">
         <v>295</v>
@@ -22230,7 +22887,7 @@
         <v>44606</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>64</v>
@@ -22254,7 +22911,7 @@
         <v>44613</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>609</v>
@@ -22265,7 +22922,7 @@
       </c>
       <c r="F72" s="21"/>
       <c r="G72" s="19" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H72" s="22" t="s">
         <v>19</v>
@@ -22278,10 +22935,10 @@
         <v>44623</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="20">
@@ -22289,7 +22946,7 @@
       </c>
       <c r="F73" s="21"/>
       <c r="G73" s="19" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H73" s="22" t="s">
         <v>19</v>
@@ -22302,7 +22959,7 @@
         <v>44629</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>64</v>
@@ -22326,7 +22983,7 @@
         <v>44631</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C75" s="19" t="s">
         <v>295</v>
@@ -22375,10 +23032,10 @@
         <v>44645</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="20">
@@ -22386,7 +23043,7 @@
       </c>
       <c r="F77" s="21"/>
       <c r="G77" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="H77" s="22" t="s">
         <v>19</v>
@@ -22399,7 +23056,7 @@
         <v>44645</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>295</v>
@@ -22452,7 +23109,7 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="E3">
-    <cfRule type="cellIs" dxfId="10" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22471,12 +23128,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Remarks xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Paid xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">Yes</Paid>
+    <Paid_x0020_by xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Expense_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Paid_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Voucher_x0020_Ref xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
+    <Accounted xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">No</Accounted>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22806,30 +23475,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Remarks xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Paid xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">Yes</Paid>
-    <Paid_x0020_by xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Expense_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Paid_x0020_date xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Voucher_x0020_Ref xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804" xsi:nil="true"/>
-    <Accounted xmlns="1aebbf00-b20e-447e-89b2-07cb1eb45804">No</Accounted>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233E6B2D-7719-43E4-8F62-6DE1F178C0C2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A25819BC-B8DE-4703-8E03-713856731CC1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1aebbf00-b20e-447e-89b2-07cb1eb45804"/>
+    <ds:schemaRef ds:uri="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22856,13 +23517,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A25819BC-B8DE-4703-8E03-713856731CC1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233E6B2D-7719-43E4-8F62-6DE1F178C0C2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1aebbf00-b20e-447e-89b2-07cb1eb45804"/>
-    <ds:schemaRef ds:uri="0e2e20c4-915d-4fd0-ac41-fe4a9dab9496"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>